--- a/wp-content/plugins/myaccount-core/docs/master-task-list.xlsx
+++ b/wp-content/plugins/myaccount-core/docs/master-task-list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookair/Work/wp-alpine-myaccount/wp-content/plugins/myaccount-core/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4A9106-9C1B-DE47-B14F-85A2243CE6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4894D8-044D-304C-97B9-ED7B0A74F74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17600" yWindow="0" windowWidth="42600" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="189">
   <si>
     <t>Order</t>
   </si>
@@ -559,13 +559,82 @@
   </si>
   <si>
     <t>Đưa tracking information tới list item ở order history. Vị trí là order meta</t>
+  </si>
+  <si>
+    <t>Order Item ở history ở mobile đang bị co lại, vì vậy ở mobile sẻ chuyển item-image và item-body thành columns</t>
+  </si>
+  <si>
+    <t>Tập trung cải thiện chất lượng của MVP thay vì tiếp tục phát triển thêm tính năng - nhằm tăng chất lượng và uy tín của sản phẩm</t>
+  </si>
+  <si>
+    <t>Cải thiện Order Item ở Order History Trên Mobile View</t>
+  </si>
+  <si>
+    <t>Cải thiện Ordetail Tracking Timeline ở view mobile</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tập trung cải thiện chất lượng của MVP thay vì tiếp tục phát triển thêm tính năng - nhằm tăng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>chất lượng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>uy tín</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> của sản phẩm</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking Time line ở mobile trông rất ngắn cũng chưa biết UI để cải thiện như thế nào ở mobile </t>
+  </si>
+  <si>
+    <t>Chuyển ma-order-status-card__step-dot thành hình tròn thay vì hình vuông</t>
+  </si>
+  <si>
+    <t>Cải thiện Popup Modal ở Mobile</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popup ở mobile nên reduce ở height đi. max-height: calc(100vh - var(--ma-space-lg) * 7); là được. </t>
+  </si>
+  <si>
+    <t>Loại bỏ javascript không cần thiết ở cho wishlist endpoint, vì ở mobile có script nào đó đang tác động đến DOM, làm thay đổi HTML khi resize/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,6 +647,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri (Body)"/>
     </font>
   </fonts>
   <fills count="4">
@@ -611,27 +696,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
@@ -948,1017 +1055,1141 @@
     <col min="10" max="10" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="50" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+    <row r="2" spans="1:10" ht="100" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="6">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="E3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6">
         <v>2</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+    <row r="4" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="E4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="6">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+    <row r="5" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
         <v>13</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="6">
         <v>4</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="7" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+    <row r="6" spans="1:10" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+      <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="8">
         <v>5</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
         <v>10</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="6">
         <v>6</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="6">
         <v>7</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="6">
         <v>8</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+    <row r="10" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="6">
         <v>9</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>21</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="11" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>21</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="E11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="6">
         <v>10</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+    <row r="12" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
         <v>16</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="E12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="6">
         <v>11</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+    <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
         <v>14</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="3">
+      <c r="E13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="6">
         <v>12</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+    <row r="14" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="6">
         <v>13</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+    <row r="15" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
         <v>15</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="E15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="6">
         <v>14</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+    <row r="16" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
         <v>18</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="3">
+      <c r="E16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="6">
         <v>15</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+    <row r="17" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
         <v>17</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="E17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="6">
         <v>16</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+    <row r="18" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
         <v>22</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="E18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="6">
         <v>17</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="7" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+    <row r="19" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
         <v>8</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="3">
+      <c r="E19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="6">
         <v>18</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
+    <row r="20" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A20" s="6">
         <v>20</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="E20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="6">
         <v>19</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
+    <row r="21" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="E21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="6">
         <v>20</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="7" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
+    <row r="22" spans="1:10" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
         <v>5</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="5">
-        <v>21</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="E22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="8">
+        <v>21</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="7" customFormat="1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
+    <row r="23" spans="1:10" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
         <v>6</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="5">
+      <c r="E23" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="8">
         <v>22</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
+    <row r="24" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A24" s="6">
         <v>4</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="E24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="6">
         <v>23</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" s="7" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
+    <row r="25" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A25" s="6">
         <v>25</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" s="3">
+      <c r="E25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" s="6">
         <v>24</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
+    <row r="26" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A26" s="6">
         <v>27</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="E26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="6">
         <v>25</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="7" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
+    <row r="27" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A27" s="6">
         <v>24</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="E27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="6">
         <v>26</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="7" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+    <row r="28" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="3">
+      <c r="E28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="6">
         <v>27</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+    <row r="29" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A29" s="6">
         <v>30</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="3">
+      <c r="E29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="6">
         <v>28</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="7" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+    <row r="30" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="3">
+      <c r="E30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="6">
         <v>29</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="J30" s="4" t="s">
+      <c r="J30" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
+    <row r="31" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A31" s="6">
         <v>28</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="3">
+      <c r="E31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="6">
         <v>30</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="1:10" ht="50" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F32" s="3">
+      <c r="E32" s="10"/>
+      <c r="F32" s="6">
         <v>1</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="7" t="s">
         <v>177</v>
       </c>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
+        <v>31</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A34" s="11">
+        <v>32</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A35" s="11">
+        <v>32</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A36" s="11">
+        <v>33</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A37" s="11">
+        <v>34</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J37" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1976,74 +2207,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>174</v>
       </c>
     </row>

--- a/wp-content/plugins/myaccount-core/docs/master-task-list.xlsx
+++ b/wp-content/plugins/myaccount-core/docs/master-task-list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookair/Work/wp-alpine-myaccount/wp-content/plugins/myaccount-core/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4894D8-044D-304C-97B9-ED7B0A74F74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3A8599-AC8F-C146-8D2F-E98A39DECF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17600" yWindow="0" windowWidth="42600" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23320" yWindow="9020" windowWidth="42600" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="194">
   <si>
     <t>Order</t>
   </si>
@@ -624,10 +624,25 @@
     <t>Global</t>
   </si>
   <si>
-    <t xml:space="preserve">Popup ở mobile nên reduce ở height đi. max-height: calc(100vh - var(--ma-space-lg) * 7); là được. </t>
-  </si>
-  <si>
-    <t>Loại bỏ javascript không cần thiết ở cho wishlist endpoint, vì ở mobile có script nào đó đang tác động đến DOM, làm thay đổi HTML khi resize/</t>
+    <t>Popup ở mobile nên reduce ở height đi. max-height: calc(100vh - var(--ma-space-lg) * 7); là được. Làm cho popup gọn hơn, user tập trung trung vào popup thay vì scale ra cả màn hình</t>
+  </si>
+  <si>
+    <t>Loại bỏ javascript không cần thiết ở cho wishlist endpoint, vì ở mobile có script nào đó đang tác động đến DOM, làm thay đổi HTML khi resize</t>
+  </si>
+  <si>
+    <t>Mục tiêu là làm đơn giản nhất ở wishlist endpoint, loại bỏ scripts không cần thiết. Giữ cho endpoint clean, simple, đồng nhất</t>
+  </si>
+  <si>
+    <t>Badge chưa thật sự có chung 1 style. Cần đồng bộ style cho badge</t>
+  </si>
+  <si>
+    <t>Mục tiêu là đồng bộ lại badge style cho nhiều badge xuất hiện trong template. Ý nghĩa giữ sự đồng nhất, và đơn giản trên toàn templates. Badge đang có mặt ở: Address Card Default badge, Default Badge ở Saved Payment, Badge có măt ở Account Stat, Badge có ở wishlist status stock, badge có ở history status</t>
+  </si>
+  <si>
+    <t>Đồng bộ UI của modal</t>
+  </si>
+  <si>
+    <t>Mục tiêu là đồng bộ layout và style của popup, mục tiêu là giữ sự đồng bộ và thống nhất của popup trên tất cả element đang sử dụng popup ui. UI nên có header gồm title, description và close popup. Phần body chứa nội dung của popup.</t>
   </si>
 </sst>
 </file>
@@ -665,7 +680,7 @@
       <name val="Calibri (Body)"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -683,6 +698,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -696,7 +717,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -723,7 +744,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -739,6 +759,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1041,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
@@ -2047,149 +2090,197 @@
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="50" x14ac:dyDescent="0.3">
-      <c r="A32" s="10"/>
-      <c r="B32" s="6" t="s">
+    <row r="32" spans="1:10" s="23" customFormat="1" ht="50" x14ac:dyDescent="0.3">
+      <c r="A32" s="20"/>
+      <c r="B32" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="E32" s="10"/>
-      <c r="F32" s="6">
+      <c r="E32" s="20"/>
+      <c r="F32" s="21">
         <v>1</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-    </row>
-    <row r="33" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
-      <c r="A33" s="11">
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+    </row>
+    <row r="33" spans="1:10" s="19" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A33" s="15">
         <v>31</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="12" t="s">
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="I33" s="12" t="s">
+      <c r="I33" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="J33" s="14"/>
-    </row>
-    <row r="34" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
-      <c r="A34" s="11">
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="1:10" s="14" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A34" s="10">
         <v>32</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="12" t="s">
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="I34" s="12" t="s">
+      <c r="I34" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="J34" s="14"/>
-    </row>
-    <row r="35" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
-      <c r="A35" s="11">
+      <c r="J34" s="13"/>
+    </row>
+    <row r="35" spans="1:10" s="14" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A35" s="10">
         <v>32</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="12" t="s">
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="I35" s="12" t="s">
+      <c r="I35" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="J35" s="14"/>
-    </row>
-    <row r="36" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
-      <c r="A36" s="11">
+      <c r="J35" s="13"/>
+    </row>
+    <row r="36" spans="1:10" s="19" customFormat="1" ht="125" x14ac:dyDescent="0.3">
+      <c r="A36" s="15">
         <v>33</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="12" t="s">
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="J36" s="14"/>
-    </row>
-    <row r="37" spans="1:10" s="15" customFormat="1" ht="100" x14ac:dyDescent="0.3">
-      <c r="A37" s="11">
+      <c r="J36" s="18"/>
+    </row>
+    <row r="37" spans="1:10" s="19" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A37" s="15">
         <v>34</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="I37" s="12" t="s">
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I37" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="J37" s="14"/>
+      <c r="J37" s="18"/>
+    </row>
+    <row r="38" spans="1:10" s="14" customFormat="1" ht="200" x14ac:dyDescent="0.3">
+      <c r="A38" s="10">
+        <v>35</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" spans="1:10" s="14" customFormat="1" ht="175" x14ac:dyDescent="0.3">
+      <c r="A39" s="10">
+        <v>36</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="J39" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/wp-content/plugins/myaccount-core/docs/master-task-list.xlsx
+++ b/wp-content/plugins/myaccount-core/docs/master-task-list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookair/Work/wp-alpine-myaccount/wp-content/plugins/myaccount-core/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3A8599-AC8F-C146-8D2F-E98A39DECF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE185E9-2A3D-5341-88BA-4C7F1C16B025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23320" yWindow="9020" windowWidth="42600" windowHeight="21380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="0" windowWidth="36140" windowHeight="24160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,25 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sales Strategy'!$A$1:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tasks!$A$1:$J$31</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="206">
   <si>
     <t>Order</t>
   </si>
@@ -644,12 +657,48 @@
   <si>
     <t>Mục tiêu là đồng bộ layout và style của popup, mục tiêu là giữ sự đồng bộ và thống nhất của popup trên tất cả element đang sử dụng popup ui. UI nên có header gồm title, description và close popup. Phần body chứa nội dung của popup.</t>
   </si>
+  <si>
+    <t>My Account Layout</t>
+  </si>
+  <si>
+    <t>Thêm width 100% vào cho ma-account-layout</t>
+  </si>
+  <si>
+    <t>Cải thiện ở trên nhiều theme</t>
+  </si>
+  <si>
+    <t>My Account Navigation</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Không tự remove những menu endpoint từ những plugin khác, nên có 1 option để can thiệp và giữ</t>
+  </si>
+  <si>
+    <t>CSS Scale font-size</t>
+  </si>
+  <si>
+    <t>Hiện tại desgin system được follow rem unit, mục đích là giữ cho khoảng cách, space, font-size.. Được scale theo html {Font-size}. Vậy để scale với nhiều theme có html khác nhau thì --ma-base nên được điều chỉnh</t>
+  </si>
+  <si>
+    <t>Khi customer có nhiều endpoint quá thì phải chuyển qua sử dụng vertical menu.</t>
+  </si>
+  <si>
+    <t>Mục tiêu là nếu My Account có nhiều endpoint quá thì phải chuyển qua Vertical My Account Navigation(Default Column đó nhé). Mục tiêu là giữ layout left navigation và right là my account content. Layout nên là 3/7 có gap. Phải viết css Mobile First, giữ Mobile Menu như hiện tại</t>
+  </si>
+  <si>
+    <t>Kỹ thuật lập trình cẩn phải thực hiện</t>
+  </si>
+  <si>
+    <t>Nên chuẩn hoá gap lại thành space-md thôi, cân bằng space ở đầu content và navigation, điều chỉnh grid lại thành 3/9</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -678,6 +727,12 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -717,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -782,6 +837,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1084,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
@@ -1096,9 +1166,10 @@
     <col min="8" max="8" width="52" customWidth="1"/>
     <col min="9" max="9" width="50" customWidth="1"/>
     <col min="10" max="10" width="46" customWidth="1"/>
+    <col min="11" max="11" width="38.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="50" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="50" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1129,8 +1200,11 @@
       <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="100" x14ac:dyDescent="0.2">
+      <c r="K1" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="100" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1162,7 +1236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>7</v>
       </c>
@@ -1194,7 +1268,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>9</v>
       </c>
@@ -1226,7 +1300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>13</v>
       </c>
@@ -1258,7 +1332,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>3</v>
       </c>
@@ -1290,7 +1364,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>10</v>
       </c>
@@ -1322,7 +1396,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>23</v>
       </c>
@@ -1354,7 +1428,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>2</v>
       </c>
@@ -1386,7 +1460,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>12</v>
       </c>
@@ -1418,7 +1492,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>21</v>
       </c>
@@ -1450,7 +1524,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>16</v>
       </c>
@@ -1482,7 +1556,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>14</v>
       </c>
@@ -1514,7 +1588,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -1546,7 +1620,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -1578,7 +1652,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="75" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>18</v>
       </c>
@@ -2114,7 +2188,7 @@
       <c r="I32" s="20"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="1:10" s="19" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" s="19" customFormat="1" ht="100" x14ac:dyDescent="0.3">
       <c r="A33" s="15">
         <v>31</v>
       </c>
@@ -2138,7 +2212,7 @@
       </c>
       <c r="J33" s="18"/>
     </row>
-    <row r="34" spans="1:10" s="14" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" s="14" customFormat="1" ht="100" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>32</v>
       </c>
@@ -2162,7 +2236,7 @@
       </c>
       <c r="J34" s="13"/>
     </row>
-    <row r="35" spans="1:10" s="14" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" s="14" customFormat="1" ht="100" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>32</v>
       </c>
@@ -2186,7 +2260,7 @@
       </c>
       <c r="J35" s="13"/>
     </row>
-    <row r="36" spans="1:10" s="19" customFormat="1" ht="125" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" s="19" customFormat="1" ht="125" x14ac:dyDescent="0.3">
       <c r="A36" s="15">
         <v>33</v>
       </c>
@@ -2210,7 +2284,7 @@
       </c>
       <c r="J36" s="18"/>
     </row>
-    <row r="37" spans="1:10" s="19" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" s="19" customFormat="1" ht="100" x14ac:dyDescent="0.3">
       <c r="A37" s="15">
         <v>34</v>
       </c>
@@ -2234,56 +2308,336 @@
       </c>
       <c r="J37" s="18"/>
     </row>
-    <row r="38" spans="1:10" s="14" customFormat="1" ht="200" x14ac:dyDescent="0.3">
-      <c r="A38" s="10">
+    <row r="38" spans="1:11" s="19" customFormat="1" ht="200" x14ac:dyDescent="0.3">
+      <c r="A38" s="15">
         <v>35</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="11" t="s">
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="J38" s="13"/>
-    </row>
-    <row r="39" spans="1:10" s="14" customFormat="1" ht="175" x14ac:dyDescent="0.3">
-      <c r="A39" s="10">
+      <c r="J38" s="18"/>
+    </row>
+    <row r="39" spans="1:11" s="19" customFormat="1" ht="175" x14ac:dyDescent="0.3">
+      <c r="A39" s="15">
         <v>36</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="11" t="s">
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="J39" s="13"/>
+      <c r="J39" s="18"/>
+    </row>
+    <row r="40" spans="1:11" s="28" customFormat="1" ht="50" x14ac:dyDescent="0.3">
+      <c r="A40" s="24">
+        <v>37</v>
+      </c>
+      <c r="B40" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="J40" s="27"/>
+    </row>
+    <row r="41" spans="1:11" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A41" s="10">
+        <v>38</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="I41" s="11"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" spans="1:11" s="14" customFormat="1" ht="150" x14ac:dyDescent="0.3">
+      <c r="A42" s="10">
+        <v>39</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D42" s="11"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="I42" s="11"/>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" spans="1:11" s="14" customFormat="1" ht="200" x14ac:dyDescent="0.3">
+      <c r="A43" s="10">
+        <v>40</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="J43" s="13"/>
+      <c r="K43" s="11"/>
+    </row>
+    <row r="44" spans="1:11" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A44" s="10">
+        <v>41</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="I44" s="11"/>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="45" spans="1:11" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="13"/>
+    </row>
+    <row r="46" spans="1:11" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="13"/>
+    </row>
+    <row r="47" spans="1:11" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="11"/>
+      <c r="J47" s="13"/>
+    </row>
+    <row r="48" spans="1:11" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="13"/>
+    </row>
+    <row r="49" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="13"/>
+    </row>
+    <row r="50" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="13"/>
+    </row>
+    <row r="51" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="13"/>
+    </row>
+    <row r="52" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="53" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="13"/>
+    </row>
+    <row r="54" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="13"/>
+    </row>
+    <row r="55" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="13"/>
+    </row>
+    <row r="56" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="13"/>
+    </row>
+    <row r="57" spans="1:10" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A57" s="10"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J31" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/wp-content/plugins/myaccount-core/docs/master-task-list.xlsx
+++ b/wp-content/plugins/myaccount-core/docs/master-task-list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookair/Work/wp-alpine-myaccount/wp-content/plugins/myaccount-core/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D59F8E-7F98-B544-A401-C9D9802B64A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B615AC-E676-A548-AA99-43E77FB8D4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="0" windowWidth="55180" windowHeight="24160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13640" yWindow="200" windowWidth="47900" windowHeight="25580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -37,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="225">
   <si>
     <t>Priority</t>
   </si>
@@ -725,6 +747,30 @@
   </si>
   <si>
     <t>Thêm Account Avatar từ kadence theme vào plugin, sau đó hide ở kadence theme đi.</t>
+  </si>
+  <si>
+    <t>Cải thiện style của ma-order-details-header</t>
+  </si>
+  <si>
+    <t>Mục tiêu là làm cho style được đồng nhất hơn, vì ở đây title quá nhỏ so với #order ID và Total. Nên cải thiện từ Mobile First trước</t>
+  </si>
+  <si>
+    <t>Track Delivery Break ở mobile</t>
+  </si>
+  <si>
+    <t>Cải thiện UI của Block Track Delivery ở Mobile, nó đang bị vỡ.</t>
+  </si>
+  <si>
+    <t>Track Delivery đang bị miss provider shipment logo</t>
+  </si>
+  <si>
+    <t>Thêm logo tới block Track Deliver giúp người dùng nhanh chóng nhận diện được shipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support WooCommerce PDF Invoices &amp; Packing Slips ở My Account </t>
+  </si>
+  <si>
+    <t>Mục tiêu là display download invoice trong order details</t>
   </si>
 </sst>
 </file>
@@ -906,6 +952,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2438,98 +2548,124 @@
       <c r="H47" s="11"/>
       <c r="I47" s="13"/>
     </row>
-    <row r="48" spans="1:10" s="14" customFormat="1" ht="50" x14ac:dyDescent="0.3">
-      <c r="A48" s="10" t="s">
+    <row r="48" spans="1:10" s="28" customFormat="1" ht="50" x14ac:dyDescent="0.3">
+      <c r="A48" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="C48" s="11"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="11" t="s">
+      <c r="C48" s="25"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="H48" s="11"/>
-      <c r="I48" s="13"/>
-    </row>
-    <row r="49" spans="1:9" s="14" customFormat="1" ht="100" x14ac:dyDescent="0.3">
-      <c r="A49" s="10" t="s">
+      <c r="H48" s="25"/>
+      <c r="I48" s="27"/>
+    </row>
+    <row r="49" spans="1:9" s="28" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A49" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="C49" s="11"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="11" t="s">
+      <c r="C49" s="25"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="H49" s="11"/>
-      <c r="I49" s="13"/>
-    </row>
-    <row r="50" spans="1:9" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
+      <c r="H49" s="25"/>
+      <c r="I49" s="27"/>
+    </row>
+    <row r="50" spans="1:9" s="28" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A50" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="C50" s="11"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="11" t="s">
+      <c r="C50" s="25"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="H50" s="11"/>
-      <c r="I50" s="13"/>
-    </row>
-    <row r="51" spans="1:9" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="27"/>
+    </row>
+    <row r="51" spans="1:9" s="14" customFormat="1" ht="100" x14ac:dyDescent="0.3">
+      <c r="A51" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>217</v>
+      </c>
       <c r="C51" s="11"/>
       <c r="D51" s="12"/>
       <c r="E51" s="12"/>
       <c r="F51" s="12"/>
-      <c r="G51" s="11"/>
+      <c r="G51" s="11" t="s">
+        <v>218</v>
+      </c>
       <c r="H51" s="11"/>
       <c r="I51" s="13"/>
     </row>
-    <row r="52" spans="1:9" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
+    <row r="52" spans="1:9" s="14" customFormat="1" ht="50" x14ac:dyDescent="0.3">
+      <c r="A52" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>219</v>
+      </c>
       <c r="C52" s="11"/>
       <c r="D52" s="12"/>
       <c r="E52" s="12"/>
       <c r="F52" s="12"/>
-      <c r="G52" s="11"/>
+      <c r="G52" s="11" t="s">
+        <v>220</v>
+      </c>
       <c r="H52" s="11"/>
       <c r="I52" s="13"/>
     </row>
-    <row r="53" spans="1:9" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
+    <row r="53" spans="1:9" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.3">
+      <c r="A53" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>221</v>
+      </c>
       <c r="C53" s="11"/>
       <c r="D53" s="12"/>
       <c r="E53" s="12"/>
       <c r="F53" s="12"/>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
+      <c r="G53" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="H53" s="11" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="I53" s="13"/>
     </row>
-    <row r="54" spans="1:9" s="14" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A54" s="10"/>
-      <c r="B54" s="11"/>
+    <row r="54" spans="1:9" s="14" customFormat="1" ht="50" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>223</v>
+      </c>
       <c r="C54" s="11"/>
       <c r="D54" s="12"/>
       <c r="E54" s="12"/>
       <c r="F54" s="12"/>
-      <c r="G54" s="11"/>
+      <c r="G54" s="11" t="s">
+        <v>224</v>
+      </c>
       <c r="H54" s="11"/>
       <c r="I54" s="13"/>
     </row>
